--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45976.375</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45976.375</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>45976.4375</v>
+        <v>45976.41666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.4375</v>
       </c>
     </row>
     <row r="20">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3825,22 +3825,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4229,22 +4229,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,22 +4633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5643,22 +5643,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6148,22 +6148,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="AC62" s="3" t="n">
-        <v>45976.52083333334</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="63">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="AC63" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.52083333334</v>
       </c>
     </row>
     <row r="64">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7649,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="AC71" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.54166666666</v>
       </c>
     </row>
     <row r="72">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8154,7 +8154,7 @@
         <v>0</v>
       </c>
       <c r="AC76" s="3" t="n">
-        <v>45976.58333333334</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="77">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -8255,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="AC77" s="3" t="n">
-        <v>45976.60416666666</v>
+        <v>45976.58333333334</v>
       </c>
     </row>
     <row r="78">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -8356,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="AC78" s="3" t="n">
-        <v>45976.61458333334</v>
+        <v>45976.60416666666</v>
       </c>
     </row>
     <row r="79">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -8457,7 +8457,7 @@
         <v>0</v>
       </c>
       <c r="AC79" s="3" t="n">
-        <v>45976.625</v>
+        <v>45976.61458333334</v>
       </c>
     </row>
     <row r="80">
@@ -8466,27 +8466,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="AC80" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.625</v>
       </c>
     </row>
     <row r="81">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8875,22 +8875,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9173,27 +9173,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="AC87" s="3" t="n">
-        <v>45976.70833333334</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="88">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9375,27 +9375,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -9443,10 +9443,10 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="AC89" s="3" t="n">
-        <v>45976.77083333334</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="90">
@@ -9476,98 +9476,199 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>2</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="3" t="n">
+        <v>45976.77083333334</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="L91" t="n">
         <v>3.4</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M91" t="n">
         <v>3.2</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N91" t="n">
         <v>2.1</v>
       </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V90" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="3" t="n">
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4532,22 +4532,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,22 +4633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8875,22 +8875,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G87" t="n">

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,22 +3724,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3926,22 +3926,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4229,22 +4229,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4532,22 +4532,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -8572,22 +8572,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G87" t="n">

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2777,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,22 +3724,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3825,22 +3825,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3926,22 +3926,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4229,22 +4229,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,22 +5239,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,22 +5441,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,22 +5946,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8305,13 +8305,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W78" t="n">
         <v>0</v>
@@ -8572,22 +8572,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G89" t="n">

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45976.375</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45976.375</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2851,13 +2851,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3219,22 +3219,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3522,22 +3522,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3623,22 +3623,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.9</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,22 +5239,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5441,22 +5441,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V51" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,22 +5946,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -6312,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6689,13 +6689,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W62" t="n">
         <v>0</v>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8875,22 +8875,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45976.375</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>45976.375</v>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2777,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2851,13 +2851,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2979,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3522,22 +3522,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3585,10 +3585,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -3623,22 +3623,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3926,22 +3926,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N36" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
         <v>2.7</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4734,22 +4734,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5239,22 +5239,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5376,13 +5376,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -6047,22 +6047,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -6312,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -6615,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6689,13 +6689,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
         <v>0</v>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8673,22 +8673,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8875,22 +8875,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2613,22 +2613,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2777,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2815,22 +2815,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2851,13 +2851,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2979,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="V28" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3585,10 +3585,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="V31" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -3623,22 +3623,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3888,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3926,22 +3926,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="V36" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4164,13 +4164,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V39" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="V42" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4734,22 +4734,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="V44" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>3.17</v>
       </c>
       <c r="N45" t="n">
-        <v>6.3</v>
+        <v>3.21</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" t="n">
         <v>1.72</v>
-      </c>
-      <c r="V45" t="n">
-        <v>2</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5174,13 +5174,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5201,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -5239,22 +5239,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5376,13 +5376,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N49" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -5403,10 +5403,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5881,13 +5881,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -5908,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -6110,10 +6110,10 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6184,13 +6184,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -6211,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W60" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -6615,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="V61" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6689,13 +6689,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W62" t="n">
         <v>0</v>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8305,13 +8305,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N78" t="n">
-        <v>3.45</v>
+        <v>3.73</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V78" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W78" t="n">
         <v>0</v>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8911,13 +8911,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -8938,10 +8938,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -8986,12 +8986,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9517,13 +9517,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M90" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="N90" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -9544,10 +9544,10 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V90" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="W90" t="n">
         <v>0</v>
@@ -9618,13 +9618,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V91" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W91" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>45976.375</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>45976.375</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2613,22 +2613,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2777,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3017,22 +3017,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3053,13 +3053,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -3118,22 +3118,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>3.58</v>
+        <v>2.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3585,10 +3585,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="V31" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -3623,22 +3623,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3659,13 +3659,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3724,22 +3724,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.53</v>
+        <v>3.09</v>
       </c>
       <c r="N34" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3888,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.73</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3926,22 +3926,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4164,13 +4164,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V37" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="V38" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.45</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1.99</v>
+        <v>3.58</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="V40" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="N42" t="n">
-        <v>5.6</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="V42" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V43" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.82</v>
+        <v>3.21</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5148,12 +5148,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
         <v>2.82</v>
@@ -5201,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="V47" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5302,10 +5302,10 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -5376,14 +5376,14 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N49" t="n">
         <v>3.5</v>
       </c>
-      <c r="N49" t="n">
-        <v>3</v>
-      </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
@@ -5403,10 +5403,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V49" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -5504,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -5605,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -5679,13 +5679,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -5706,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5881,13 +5881,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -5908,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M56" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N56" t="n">
-        <v>3.97</v>
+        <v>2.67</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -6110,10 +6110,10 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V56" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6184,13 +6184,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -6211,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.99</v>
+        <v>1.49</v>
       </c>
       <c r="M59" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="N59" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="V59" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -6615,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6689,37 +6689,37 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V62" t="n">
         <v>1.9</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N62" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.75</v>
       </c>
       <c r="W62" t="n">
         <v>0</v>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8673,22 +8673,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -8810,13 +8810,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -8837,10 +8837,10 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W83" t="n">
         <v>0</v>
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8911,13 +8911,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -8938,10 +8938,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -8976,22 +8976,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9077,22 +9077,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9178,22 +9178,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AI91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,55 +528,85 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -679,7 +709,25 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>45976.08333333334</v>
       </c>
     </row>
@@ -780,7 +828,25 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>45976.33333333334</v>
       </c>
     </row>
@@ -858,30 +924,48 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.75</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AB4" t="n">
         <v>2.05</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>45976.375</v>
       </c>
     </row>
@@ -982,7 +1066,25 @@
       <c r="AB5" t="n">
         <v>0</v>
       </c>
-      <c r="AC5" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45976.375</v>
       </c>
     </row>
@@ -1083,7 +1185,25 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45976.375</v>
       </c>
     </row>
@@ -1184,7 +1304,25 @@
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" s="3" t="n">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45976.39583333334</v>
       </c>
     </row>
@@ -1285,7 +1423,25 @@
       <c r="AB8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>45976.41666666666</v>
       </c>
     </row>
@@ -1386,7 +1542,25 @@
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>45976.41666666666</v>
       </c>
     </row>
@@ -1487,7 +1661,25 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>45976.41666666666</v>
       </c>
     </row>
@@ -1588,7 +1780,25 @@
       <c r="AB11" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="3" t="n">
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>45976.41666666666</v>
       </c>
     </row>
@@ -1689,7 +1899,25 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" s="3" t="n">
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>45976.41666666666</v>
       </c>
     </row>
@@ -1790,7 +2018,25 @@
       <c r="AB13" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" s="3" t="n">
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -1891,7 +2137,25 @@
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="n">
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -1992,7 +2256,25 @@
       <c r="AB15" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="n">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -2093,7 +2375,25 @@
       <c r="AB16" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="3" t="n">
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -2194,7 +2494,25 @@
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AC17" s="3" t="n">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -2295,7 +2613,25 @@
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="3" t="n">
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -2396,7 +2732,25 @@
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="3" t="n">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
       </c>
     </row>
@@ -2497,7 +2851,25 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="n">
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -2575,30 +2947,48 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.95</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AB21" t="n">
         <v>1.75</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="3" t="n">
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -2676,30 +3066,48 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.73</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AB22" t="n">
         <v>2</v>
       </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="n">
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -2777,30 +3185,48 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.08</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AB23" t="n">
         <v>1.65</v>
       </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3" t="n">
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -2901,7 +3327,25 @@
       <c r="AB24" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="n">
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3002,7 +3446,25 @@
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="3" t="n">
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3080,30 +3542,48 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.81</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AB26" t="n">
         <v>1.89</v>
       </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3" t="n">
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3204,7 +3684,25 @@
       <c r="AB27" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="3" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3282,30 +3780,48 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.12</v>
       </c>
-      <c r="V28" t="n">
+      <c r="AB28" t="n">
         <v>1.64</v>
       </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="3" t="n">
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3383,30 +3899,48 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.78</v>
       </c>
-      <c r="V29" t="n">
+      <c r="AB29" t="n">
         <v>1.92</v>
       </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="n">
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3484,30 +4018,48 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.1</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AB30" t="n">
         <v>1.65</v>
       </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="3" t="n">
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3585,30 +4137,48 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1.92</v>
       </c>
-      <c r="V31" t="n">
+      <c r="AB31" t="n">
         <v>1.78</v>
       </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="3" t="n">
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3686,30 +4256,48 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.95</v>
       </c>
-      <c r="V32" t="n">
+      <c r="AB32" t="n">
         <v>1.75</v>
       </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3" t="n">
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3810,7 +4398,25 @@
       <c r="AB33" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="3" t="n">
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -3888,30 +4494,48 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.97</v>
       </c>
-      <c r="V34" t="n">
+      <c r="AB34" t="n">
         <v>1.73</v>
       </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="3" t="n">
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4012,7 +4636,25 @@
       <c r="AB35" t="n">
         <v>0</v>
       </c>
-      <c r="AC35" s="3" t="n">
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4113,7 +4755,25 @@
       <c r="AB36" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" s="3" t="n">
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4191,30 +4851,48 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.02</v>
       </c>
-      <c r="V37" t="n">
+      <c r="AB37" t="n">
         <v>1.7</v>
       </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="3" t="n">
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4292,30 +4970,48 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
         <v>1.58</v>
       </c>
-      <c r="V38" t="n">
+      <c r="AB38" t="n">
         <v>2.2</v>
       </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="3" t="n">
+      <c r="AC38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4416,7 +5112,25 @@
       <c r="AB39" t="n">
         <v>0</v>
       </c>
-      <c r="AC39" s="3" t="n">
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4494,30 +5208,48 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
         <v>1.82</v>
       </c>
-      <c r="V40" t="n">
+      <c r="AB40" t="n">
         <v>1.88</v>
       </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="3" t="n">
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4618,7 +5350,25 @@
       <c r="AB41" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="3" t="n">
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4696,30 +5446,48 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1.77</v>
       </c>
-      <c r="V42" t="n">
+      <c r="AB42" t="n">
         <v>1.93</v>
       </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="3" t="n">
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4797,30 +5565,48 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
         <v>1.8</v>
       </c>
-      <c r="V43" t="n">
+      <c r="AB43" t="n">
         <v>1.9</v>
       </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="3" t="n">
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4898,30 +5684,48 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
         <v>1.87</v>
       </c>
-      <c r="V44" t="n">
+      <c r="AB44" t="n">
         <v>1.83</v>
       </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3" t="n">
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -4999,30 +5803,48 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
         <v>1.8</v>
       </c>
-      <c r="V45" t="n">
+      <c r="AB45" t="n">
         <v>1.9</v>
       </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3" t="n">
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5100,30 +5922,48 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2</v>
       </c>
-      <c r="V46" t="n">
+      <c r="AB46" t="n">
         <v>1.72</v>
       </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="3" t="n">
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5201,30 +6041,48 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
         <v>2.1</v>
       </c>
-      <c r="V47" t="n">
+      <c r="AB47" t="n">
         <v>1.65</v>
       </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3" t="n">
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5302,30 +6160,48 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
         <v>1.85</v>
       </c>
-      <c r="V48" t="n">
+      <c r="AB48" t="n">
         <v>1.85</v>
       </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="3" t="n">
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5403,30 +6279,48 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
         <v>1.85</v>
       </c>
-      <c r="V49" t="n">
+      <c r="AB49" t="n">
         <v>1.95</v>
       </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3" t="n">
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5504,30 +6398,48 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
         <v>1.98</v>
       </c>
-      <c r="V50" t="n">
+      <c r="AB50" t="n">
         <v>1.72</v>
       </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="3" t="n">
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5605,30 +6517,48 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
         <v>2.13</v>
       </c>
-      <c r="V51" t="n">
+      <c r="AB51" t="n">
         <v>1.64</v>
       </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="3" t="n">
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5706,30 +6636,48 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
         <v>1.76</v>
       </c>
-      <c r="V52" t="n">
+      <c r="AB52" t="n">
         <v>1.94</v>
       </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="n">
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5807,30 +6755,48 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
         <v>1.77</v>
       </c>
-      <c r="V53" t="n">
+      <c r="AB53" t="n">
         <v>1.93</v>
       </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="3" t="n">
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -5931,7 +6897,25 @@
       <c r="AB54" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" s="3" t="n">
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6009,30 +6993,48 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
         <v>1.95</v>
       </c>
-      <c r="V55" t="n">
+      <c r="AB55" t="n">
         <v>1.75</v>
       </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="3" t="n">
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6110,30 +7112,48 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
         <v>1.92</v>
       </c>
-      <c r="V56" t="n">
+      <c r="AB56" t="n">
         <v>1.78</v>
       </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="3" t="n">
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6234,7 +7254,25 @@
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="3" t="n">
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6335,7 +7373,25 @@
       <c r="AB58" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" s="3" t="n">
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6413,30 +7469,48 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
         <v>1.72</v>
       </c>
-      <c r="V59" t="n">
+      <c r="AB59" t="n">
         <v>2</v>
       </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3" t="n">
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6537,7 +7611,25 @@
       <c r="AB60" t="n">
         <v>0</v>
       </c>
-      <c r="AC60" s="3" t="n">
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6638,7 +7730,25 @@
       <c r="AB61" t="n">
         <v>0</v>
       </c>
-      <c r="AC61" s="3" t="n">
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6716,30 +7826,48 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
         <v>1.8</v>
       </c>
-      <c r="V62" t="n">
+      <c r="AB62" t="n">
         <v>1.9</v>
       </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="n">
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3" t="n">
         <v>45976.5</v>
       </c>
     </row>
@@ -6840,7 +7968,25 @@
       <c r="AB63" t="n">
         <v>0</v>
       </c>
-      <c r="AC63" s="3" t="n">
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3" t="n">
         <v>45976.52083333334</v>
       </c>
     </row>
@@ -6941,7 +8087,25 @@
       <c r="AB64" t="n">
         <v>0</v>
       </c>
-      <c r="AC64" s="3" t="n">
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7042,7 +8206,25 @@
       <c r="AB65" t="n">
         <v>0</v>
       </c>
-      <c r="AC65" s="3" t="n">
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7143,7 +8325,25 @@
       <c r="AB66" t="n">
         <v>0</v>
       </c>
-      <c r="AC66" s="3" t="n">
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7244,7 +8444,25 @@
       <c r="AB67" t="n">
         <v>0</v>
       </c>
-      <c r="AC67" s="3" t="n">
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7345,7 +8563,25 @@
       <c r="AB68" t="n">
         <v>0</v>
       </c>
-      <c r="AC68" s="3" t="n">
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7446,7 +8682,25 @@
       <c r="AB69" t="n">
         <v>0</v>
       </c>
-      <c r="AC69" s="3" t="n">
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7547,7 +8801,25 @@
       <c r="AB70" t="n">
         <v>0</v>
       </c>
-      <c r="AC70" s="3" t="n">
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7648,7 +8920,25 @@
       <c r="AB71" t="n">
         <v>0</v>
       </c>
-      <c r="AC71" s="3" t="n">
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3" t="n">
         <v>45976.54166666666</v>
       </c>
     </row>
@@ -7749,7 +9039,25 @@
       <c r="AB72" t="n">
         <v>0</v>
       </c>
-      <c r="AC72" s="3" t="n">
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3" t="n">
         <v>45976.5625</v>
       </c>
     </row>
@@ -7850,7 +9158,25 @@
       <c r="AB73" t="n">
         <v>0</v>
       </c>
-      <c r="AC73" s="3" t="n">
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3" t="n">
         <v>45976.5625</v>
       </c>
     </row>
@@ -7951,7 +9277,25 @@
       <c r="AB74" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" s="3" t="n">
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3" t="n">
         <v>45976.5625</v>
       </c>
     </row>
@@ -8052,7 +9396,25 @@
       <c r="AB75" t="n">
         <v>0</v>
       </c>
-      <c r="AC75" s="3" t="n">
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3" t="n">
         <v>45976.5625</v>
       </c>
     </row>
@@ -8153,7 +9515,25 @@
       <c r="AB76" t="n">
         <v>0</v>
       </c>
-      <c r="AC76" s="3" t="n">
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3" t="n">
         <v>45976.5625</v>
       </c>
     </row>
@@ -8254,7 +9634,25 @@
       <c r="AB77" t="n">
         <v>0</v>
       </c>
-      <c r="AC77" s="3" t="n">
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3" t="n">
         <v>45976.58333333334</v>
       </c>
     </row>
@@ -8332,30 +9730,48 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
         <v>1.93</v>
       </c>
-      <c r="V78" t="n">
+      <c r="AB78" t="n">
         <v>1.77</v>
       </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="3" t="n">
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="3" t="n">
         <v>45976.60416666666</v>
       </c>
     </row>
@@ -8456,7 +9872,25 @@
       <c r="AB79" t="n">
         <v>0</v>
       </c>
-      <c r="AC79" s="3" t="n">
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="3" t="n">
         <v>45976.61458333334</v>
       </c>
     </row>
@@ -8557,7 +9991,25 @@
       <c r="AB80" t="n">
         <v>0</v>
       </c>
-      <c r="AC80" s="3" t="n">
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="3" t="n">
         <v>45976.625</v>
       </c>
     </row>
@@ -8658,7 +10110,25 @@
       <c r="AB81" t="n">
         <v>0</v>
       </c>
-      <c r="AC81" s="3" t="n">
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -8759,7 +10229,25 @@
       <c r="AB82" t="n">
         <v>0</v>
       </c>
-      <c r="AC82" s="3" t="n">
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -8837,30 +10325,48 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
         <v>2</v>
       </c>
-      <c r="V83" t="n">
+      <c r="AB83" t="n">
         <v>1.72</v>
       </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="3" t="n">
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -8961,7 +10467,25 @@
       <c r="AB84" t="n">
         <v>0</v>
       </c>
-      <c r="AC84" s="3" t="n">
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -9062,7 +10586,25 @@
       <c r="AB85" t="n">
         <v>0</v>
       </c>
-      <c r="AC85" s="3" t="n">
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -9163,7 +10705,25 @@
       <c r="AB86" t="n">
         <v>0</v>
       </c>
-      <c r="AC86" s="3" t="n">
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -9264,7 +10824,25 @@
       <c r="AB87" t="n">
         <v>0</v>
       </c>
-      <c r="AC87" s="3" t="n">
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3" t="n">
         <v>45976.6875</v>
       </c>
     </row>
@@ -9365,7 +10943,25 @@
       <c r="AB88" t="n">
         <v>0</v>
       </c>
-      <c r="AC88" s="3" t="n">
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3" t="n">
         <v>45976.70833333334</v>
       </c>
     </row>
@@ -9466,7 +11062,25 @@
       <c r="AB89" t="n">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="n">
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="n">
         <v>45976.70833333334</v>
       </c>
     </row>
@@ -9544,30 +11158,48 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
         <v>1.96</v>
       </c>
-      <c r="V90" t="n">
+      <c r="AB90" t="n">
         <v>1.74</v>
       </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="3" t="n">
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="3" t="n">
         <v>45976.77083333334</v>
       </c>
     </row>
@@ -9645,30 +11277,48 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
         <v>2.02</v>
       </c>
-      <c r="V91" t="n">
+      <c r="AB91" t="n">
         <v>1.8</v>
       </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="3" t="n">
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,55 +2920,55 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.82</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.36</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>5.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.74</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>5.6</v>
+        <v>2.57</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="M37" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="N37" t="n">
-        <v>3.13</v>
+        <v>2.36</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>1.63</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="N46" t="n">
-        <v>3.21</v>
+        <v>3.97</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB46" t="n">
         <v>1.72</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.31</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="N47" t="n">
-        <v>2.82</v>
+        <v>6.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.68</v>
+        <v>2.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="N50" t="n">
-        <v>3.97</v>
+        <v>2.45</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.21</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>5.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>1.63</v>
+        <v>3.58</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N55" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M58" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="N58" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.02</v>
+        <v>3.45</v>
       </c>
       <c r="M62" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,55 +897,55 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.58</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="M32" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="M42" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="N43" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.4</v>
+        <v>2.34</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="N44" t="n">
-        <v>1.63</v>
+        <v>2.57</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="M46" t="n">
-        <v>3.23</v>
+        <v>2.92</v>
       </c>
       <c r="N46" t="n">
-        <v>3.97</v>
+        <v>2.36</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M47" t="n">
-        <v>4.6</v>
+        <v>3.68</v>
       </c>
       <c r="N47" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="N50" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>2.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="N52" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>1.63</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="M55" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="N55" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="M58" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="M61" t="n">
-        <v>3.41</v>
+        <v>3.53</v>
       </c>
       <c r="N61" t="n">
-        <v>4.2</v>
+        <v>3.39</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="M29" t="n">
-        <v>4.6</v>
+        <v>3.07</v>
       </c>
       <c r="N29" t="n">
-        <v>6.6</v>
+        <v>3.13</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.45</v>
+        <v>2.21</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="M35" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>2.82</v>
       </c>
       <c r="M38" t="n">
-        <v>3.41</v>
+        <v>2.92</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="M46" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N46" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
         <v>5.6</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="M51" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N51" t="n">
-        <v>3.97</v>
+        <v>6.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="M52" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.84</v>
+        <v>2.31</v>
       </c>
       <c r="M61" t="n">
-        <v>3.53</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.39</v>
+        <v>2.82</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="N85" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G87" t="n">

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>4.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.39</v>
+        <v>1.63</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
         <v>2.82</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>3.21</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="M37" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>3.21</v>
+        <v>3.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.82</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.36</v>
+        <v>3.58</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>3.74</v>
+        <v>5.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,55 +5419,55 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.45</v>
+        <v>2.32</v>
       </c>
       <c r="M46" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="N46" t="n">
-        <v>1.99</v>
+        <v>2.67</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N47" t="n">
         <v>3.8</v>
-      </c>
-      <c r="N47" t="n">
-        <v>5.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="M51" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>6.6</v>
+        <v>2.82</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.4</v>
+        <v>2.02</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="N54" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N57" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.09</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N60" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="M62" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="M85" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="N85" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10575,16 +10575,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA85" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11012,55 +11012,55 @@
         </is>
       </c>
       <c r="L89" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
         <v>1.75</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>0</v>
-      </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N91" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI91"/>
+  <dimension ref="A1:AI88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45976.39583333334</v>
+        <v>45976.375</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45976.41666666666</v>
+        <v>45976.375</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45976.41666666666</v>
+        <v>45976.375</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45976.41666666666</v>
+        <v>45976.39583333334</v>
       </c>
     </row>
     <row r="11">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>45976.4375</v>
+        <v>45976.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>45976.4375</v>
+        <v>45976.41666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>45976.4375</v>
+        <v>45976.41666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.4375</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.4375</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.4375</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.09</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M37" t="n">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="N37" t="n">
-        <v>3.74</v>
+        <v>2.67</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.92</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,55 +4943,55 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
         <v>1.8</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.13</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.68</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3.97</v>
+        <v>6.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M46" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="N46" t="n">
-        <v>2.67</v>
+        <v>3.13</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="N47" t="n">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N50" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="M54" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="N54" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="M55" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="N55" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>45976.52083333334</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="64">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="66">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.52083333334</v>
       </c>
     </row>
     <row r="67">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="70">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="71">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="72">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.58333333334</v>
       </c>
     </row>
     <row r="75">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.61458333334</v>
       </c>
     </row>
     <row r="77">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>45976.58333333334</v>
+        <v>45976.625</v>
       </c>
     </row>
     <row r="78">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M78" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45976.60416666666</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="79">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>45976.61458333334</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="80">
@@ -9900,27 +9900,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>45976.625</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="81">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="N81" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="M83" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>7.8</v>
+        <v>2.75</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="M84" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>3.23</v>
+        <v>4.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10495,27 +10495,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="M85" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="N85" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10575,16 +10575,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="86">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="87">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.55</v>
+        <v>10</v>
       </c>
       <c r="M87" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N87" t="n">
-        <v>2.75</v>
+        <v>1.28</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.77083333334</v>
       </c>
     </row>
     <row r="88">
@@ -10852,27 +10852,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,363 +10962,6 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>45976.70833333334</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Spain Segunda División</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Granada CF</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="M89" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI89" s="3" t="n">
-        <v>45976.70833333334</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>10</v>
-      </c>
-      <c r="M90" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI90" s="3" t="n">
-        <v>45976.77083333334</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI91" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="N23" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB33" t="n">
         <v>1.65</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N34" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.18</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.67</v>
+        <v>6.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>6.6</v>
+        <v>1.63</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.11</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.13</v>
+        <v>1.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="M47" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="N47" t="n">
-        <v>3.39</v>
+        <v>3.74</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="N48" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,14 +6490,14 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.5</v>
       </c>
-      <c r="N51" t="n">
-        <v>3</v>
-      </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="M55" t="n">
-        <v>2.91</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>3.8</v>
+        <v>1.99</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9742,16 +9742,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.4</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>7.8</v>
+        <v>2.75</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10218,16 +10218,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI88"/>
+  <dimension ref="A1:AI89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.17</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.21</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.39</v>
+        <v>3.58</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>2.82</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB31" t="n">
         <v>1.65</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.82</v>
+        <v>1.68</v>
       </c>
       <c r="M33" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.36</v>
+        <v>4.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>2.31</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>6.6</v>
+        <v>2.82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>2.82</v>
+        <v>3.97</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N46" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="M47" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M49" t="n">
         <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="M50" t="n">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="N50" t="n">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>45976.5</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.55</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,14 +7561,14 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N60" t="n">
         <v>3.45</v>
       </c>
-      <c r="M60" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1.99</v>
-      </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,16 +7963,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AI75" s="3" t="n">
-        <v>45976.60416666666</v>
+        <v>45976.58333333334</v>
       </c>
     </row>
     <row r="76">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>45976.61458333334</v>
+        <v>45976.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>45976.625</v>
+        <v>45976.61458333334</v>
       </c>
     </row>
     <row r="78">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.625</v>
       </c>
     </row>
     <row r="79">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N82" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10218,16 +10218,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10495,27 +10495,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="M85" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="N85" t="n">
-        <v>3.98</v>
+        <v>7.8</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>45976.70833333334</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="86">
@@ -10733,27 +10733,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>10</v>
+        <v>1.83</v>
       </c>
       <c r="M87" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="N87" t="n">
-        <v>1.28</v>
+        <v>3.98</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>45976.77083333334</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="88">
@@ -10852,116 +10852,235 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3" t="n">
+        <v>45976.77083333334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L88" t="n">
+      <c r="L89" t="n">
         <v>3.96</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M89" t="n">
         <v>3.35</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N89" t="n">
         <v>1.76</v>
       </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="n">
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB88" t="n">
+      <c r="AB89" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI88" s="3" t="n">
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI89"/>
+  <dimension ref="A1:AI90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,55 +1254,55 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.58</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.53</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.39</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>3.13</v>
+        <v>4.7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.09</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.49</v>
+        <v>4.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.97</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="M45" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="N45" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="M46" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N49" t="n">
-        <v>5.6</v>
+        <v>3.97</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="M50" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.67</v>
+        <v>4.3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M51" t="n">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="N51" t="n">
-        <v>3.74</v>
+        <v>2.67</v>
       </c>
       <c r="O51" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.78</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC51" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>45976.5</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.4</v>
+        <v>2.11</v>
       </c>
       <c r="M59" t="n">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="N59" t="n">
-        <v>1.63</v>
+        <v>3.13</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7795,77 +7795,77 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
-        <v>45976.52083333334</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="67">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.52083333334</v>
       </c>
     </row>
     <row r="68">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9186,27 +9186,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>45976.58333333334</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="75">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>45976.60416666666</v>
+        <v>45976.58333333334</v>
       </c>
     </row>
     <row r="77">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>45976.61458333334</v>
+        <v>45976.60416666666</v>
       </c>
     </row>
     <row r="78">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45976.625</v>
+        <v>45976.61458333334</v>
       </c>
     </row>
     <row r="79">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.625</v>
       </c>
     </row>
     <row r="80">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,55 +10179,55 @@
         </is>
       </c>
       <c r="L82" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB82" t="n">
         <v>1.55</v>
-      </c>
-      <c r="M82" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N82" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.77</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M85" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>7.8</v>
+        <v>2.75</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10614,27 +10614,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>45976.70833333334</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="87">
@@ -10852,27 +10852,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>45976.77083333334</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="89">
@@ -10971,116 +10971,235 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>10</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="n">
+        <v>45976.77083333334</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L89" t="n">
+      <c r="L90" t="n">
         <v>3.96</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M90" t="n">
         <v>3.35</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N90" t="n">
         <v>1.76</v>
       </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB89" t="n">
+      <c r="AB90" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI89" s="3" t="n">
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.45</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.6</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>3.21</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>4.7</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.09</v>
       </c>
       <c r="N35" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,55 +4705,55 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.9</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N38" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="N40" t="n">
-        <v>1.63</v>
+        <v>2.36</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="M48" t="n">
         <v>3.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="M49" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>2.67</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.49</v>
+        <v>4.4</v>
       </c>
       <c r="M53" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB53" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>2.82</v>
+        <v>3.97</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="M55" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="N55" t="n">
-        <v>3.21</v>
+        <v>2.67</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="M56" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="M57" t="n">
-        <v>3.09</v>
+        <v>3.53</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.11</v>
+        <v>3.45</v>
       </c>
       <c r="M59" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
         <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7795,77 +7795,77 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="M63" t="n">
-        <v>3.53</v>
+        <v>2.91</v>
       </c>
       <c r="N63" t="n">
-        <v>3.39</v>
+        <v>2.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8033,77 +8033,77 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="M64" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="N64" t="n">
-        <v>6.6</v>
+        <v>3.74</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>45976.5</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="M65" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.76</v>
+        <v>2.77</v>
       </c>
       <c r="M82" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="N82" t="n">
-        <v>4.1</v>
+        <v>2.37</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10218,16 +10218,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N85" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10575,16 +10575,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M86" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="N86" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -668,40 +668,40 @@
         <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA2" t="n">
         <v>2.08</v>
@@ -710,22 +710,22 @@
         <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45976.08333333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.07</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>3.13</v>
+        <v>46</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>3.13</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
         <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.09</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,14 +4824,14 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N37" t="n">
         <v>3.25</v>
       </c>
-      <c r="N37" t="n">
-        <v>1.8</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M41" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="N41" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>3.21</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>3.41</v>
       </c>
       <c r="N53" t="n">
-        <v>1.63</v>
+        <v>3.74</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N54" t="n">
-        <v>3.97</v>
+        <v>2.67</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M55" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="N55" t="n">
-        <v>2.67</v>
+        <v>3.13</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>2.82</v>
       </c>
       <c r="M57" t="n">
-        <v>3.53</v>
+        <v>2.92</v>
       </c>
       <c r="N57" t="n">
-        <v>3.39</v>
+        <v>2.36</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>5.2</v>
+        <v>2.82</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8033,77 +8033,77 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.74</v>
+        <v>1.63</v>
       </c>
       <c r="O64" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>45976.5</v>
@@ -8120,22 +8120,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>3.8</v>
+        <v>1.79</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,22 +9429,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.77</v>
+        <v>1.76</v>
       </c>
       <c r="M82" t="n">
-        <v>2.98</v>
+        <v>3.23</v>
       </c>
       <c r="N82" t="n">
-        <v>2.37</v>
+        <v>4.1</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10218,16 +10218,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="M84" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>3.23</v>
+        <v>5.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.76</v>
+        <v>2.77</v>
       </c>
       <c r="M85" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="N85" t="n">
-        <v>4.1</v>
+        <v>2.37</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10575,16 +10575,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI90"/>
+  <dimension ref="A1:AI89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,27 +856,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45976.375</v>
+        <v>45976.33333333334</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,55 +1492,55 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45976.39583333334</v>
+        <v>45976.375</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45976.41666666666</v>
+        <v>45976.39583333334</v>
       </c>
     </row>
     <row r="12">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>45976.4375</v>
+        <v>45976.41666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>45976.45833333334</v>
+        <v>45976.4375</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>45976.5</v>
+        <v>45976.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.53</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>3.39</v>
+        <v>2.57</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>1.68</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.45</v>
+        <v>2.82</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="N37" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="N39" t="n">
-        <v>2.82</v>
+        <v>2.36</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB39" t="n">
         <v>1.65</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="M41" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>2.48</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="M53" t="n">
-        <v>3.41</v>
+        <v>2.91</v>
       </c>
       <c r="N53" t="n">
-        <v>3.74</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,55 +6847,55 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
         <v>2.32</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB54" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="M55" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,14 +7085,14 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="M56" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N56" t="n">
         <v>5.6</v>
       </c>
-      <c r="N56" t="n">
-        <v>10</v>
-      </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="M57" t="n">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="N57" t="n">
-        <v>2.36</v>
+        <v>3.74</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>45976.5</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M58" t="n">
         <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.79</v>
+        <v>2.32</v>
       </c>
       <c r="M61" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N61" t="n">
-        <v>3.97</v>
+        <v>2.67</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.45</v>
+        <v>2.21</v>
       </c>
       <c r="M62" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,14 +8037,14 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="M64" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N64" t="n">
         <v>4.2</v>
       </c>
-      <c r="N64" t="n">
-        <v>1.63</v>
-      </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
-        <v>45976.52083333334</v>
+        <v>45976.5</v>
       </c>
     </row>
     <row r="68">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="AI68" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.52083333334</v>
       </c>
     </row>
     <row r="69">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8701,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AI69" s="3" t="n">
-        <v>45976.54166666666</v>
+        <v>45976.5625</v>
       </c>
     </row>
     <row r="70">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9186,27 +9186,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AI74" s="3" t="n">
-        <v>45976.5625</v>
+        <v>45976.58333333334</v>
       </c>
     </row>
     <row r="75">
@@ -9424,27 +9424,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="AI76" s="3" t="n">
-        <v>45976.58333333334</v>
+        <v>45976.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AI77" s="3" t="n">
-        <v>45976.60416666666</v>
+        <v>45976.61458333334</v>
       </c>
     </row>
     <row r="78">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
-        <v>45976.61458333334</v>
+        <v>45976.625</v>
       </c>
     </row>
     <row r="79">
@@ -9781,27 +9781,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>45976.625</v>
+        <v>45976.6875</v>
       </c>
     </row>
     <row r="80">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="M82" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N82" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10218,16 +10218,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.55</v>
+        <v>2.77</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="N84" t="n">
-        <v>5.2</v>
+        <v>2.37</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.77</v>
+        <v>2.16</v>
       </c>
       <c r="M85" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="N85" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>45976.6875</v>
+        <v>45976.70833333334</v>
       </c>
     </row>
     <row r="87">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10852,27 +10852,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>45976.70833333334</v>
+        <v>45976.77083333334</v>
       </c>
     </row>
     <row r="89">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>10</v>
+        <v>3.96</v>
       </c>
       <c r="M89" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11081,125 +11081,6 @@
         <v>0</v>
       </c>
       <c r="AI89" s="3" t="n">
-        <v>45976.77083333334</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="M90" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI90" s="3" t="n">
         <v>45976.875</v>
       </c>
     </row>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -677,7 +677,7 @@
         <v>4.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>45976.5</v>
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M55" t="n">
         <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45976.5</v>
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M58" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>45976.5</v>
@@ -7442,49 +7442,49 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M59" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA59" t="n">
         <v>1.58</v>
@@ -7493,22 +7493,22 @@
         <v>2.2</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>45976.5</v>
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>4.7</v>
+        <v>5.07</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>45976.5</v>
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M66" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V66" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC66" t="n">
         <v>3.4</v>
       </c>
-      <c r="N66" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45976.5</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45976.08333333334</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1073,16 +1073,16 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45976.375</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45976.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45976.39583333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>4.18</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>4.99</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.01</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45976.4375</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45976.4375</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>3.55</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>2.04</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45976.4375</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M26" t="n">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45976.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45976.5</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45976.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="M29" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.21</v>
+        <v>5.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45976.5</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA30" t="n">
         <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45976.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45976.5</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z32" t="n">
         <v>3.6</v>
       </c>
-      <c r="N32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45976.5</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>4.24</v>
       </c>
       <c r="M34" t="n">
-        <v>3.53</v>
+        <v>4.11</v>
       </c>
       <c r="N34" t="n">
-        <v>3.39</v>
+        <v>1.62</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45976.5</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45976.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>1.74</v>
       </c>
       <c r="M37" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>3.13</v>
+        <v>4.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45976.5</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>1.18</v>
       </c>
       <c r="M38" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.13</v>
+        <v>1.49</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.64</v>
+        <v>2.28</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.36</v>
+        <v>4.61</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>45976.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45976.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>45976.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>45976.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45976.5</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3.58</v>
+        <v>6.5</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>45976.5</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45976.5</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.4</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>45976.5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>45976.5</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O52" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P52" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R52" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="T52" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U52" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V52" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="W52" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.09</v>
+        <v>2.94</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.17</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
         <v>1.3</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>45976.5</v>
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="M53" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
         <v>2.5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="M54" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,61 +6966,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>6.5</v>
+        <v>3.27</v>
       </c>
       <c r="O55" t="n">
-        <v>1.89</v>
+        <v>2.74</v>
       </c>
       <c r="P55" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="R55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V55" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y55" t="n">
         <v>1.32</v>
       </c>
-      <c r="S55" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V55" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z55" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.67</v>
+        <v>3.54</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AE55" t="n">
         <v>1.83</v>
@@ -7029,10 +7029,10 @@
         <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45976.5</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="M56" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>2.48</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.79</v>
+        <v>4.49</v>
       </c>
       <c r="M57" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="N57" t="n">
-        <v>3.74</v>
+        <v>1.8</v>
       </c>
       <c r="O57" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="P57" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S57" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="T57" t="n">
-        <v>2.35</v>
+        <v>3.29</v>
       </c>
       <c r="U57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V57" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y57" t="n">
         <v>1.44</v>
       </c>
-      <c r="V57" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z57" t="n">
-        <v>3.74</v>
+        <v>2.56</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.78</v>
+        <v>2.39</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AF57" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>45976.5</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N58" t="n">
-        <v>6.2</v>
+        <v>5.07</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="P58" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
         <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T58" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U58" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V58" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X58" t="n">
         <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AD58" t="n">
         <v>1.28</v>
       </c>
       <c r="AE58" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>45976.5</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="O59" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="Q59" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S59" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="T59" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="U59" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V59" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="W59" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X59" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH59" t="n">
-        <v>3.38</v>
+        <v>2.41</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>45976.5</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="N60" t="n">
-        <v>5.07</v>
+        <v>3.64</v>
       </c>
       <c r="O60" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>4.47</v>
       </c>
       <c r="R60" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S60" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T60" t="n">
         <v>2.8</v>
       </c>
       <c r="U60" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V60" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W60" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X60" t="n">
         <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC60" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>45976.5</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.21</v>
+        <v>1.26</v>
       </c>
       <c r="M62" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>11</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S62" t="n">
         <v>3.2</v>
       </c>
-      <c r="N62" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>45976.5</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M64" t="n">
-        <v>3.41</v>
+        <v>3.72</v>
       </c>
       <c r="N64" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q64" t="n">
         <v>4.2</v>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>45976.5</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="M66" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>3.64</v>
+        <v>2.81</v>
       </c>
       <c r="O66" t="n">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="P66" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.47</v>
+        <v>3.52</v>
       </c>
       <c r="R66" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S66" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T66" t="n">
         <v>2.8</v>
       </c>
       <c r="U66" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V66" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="W66" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y66" t="n">
         <v>1.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA66" t="n">
         <v>1.98</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45976.5</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.6</v>
+        <v>2.63</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45976.5</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45976.5625</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>45976.5625</v>
@@ -8998,64 +8998,64 @@
         <v>2.55</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45976.5625</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45976.5625</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9474,40 +9474,40 @@
         <v>3.73</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA76" t="n">
         <v>1.93</v>
@@ -9516,22 +9516,22 @@
         <v>1.77</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45976.60416666666</v>
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45976.61458333334</v>
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.76</v>
+        <v>2.77</v>
       </c>
       <c r="M79" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="N79" t="n">
-        <v>4.1</v>
+        <v>2.37</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45976.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45976.6875</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N81" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45976.6875</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M82" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10307,40 +10307,40 @@
         <v>7.8</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA83" t="n">
         <v>2.05</v>
@@ -10349,22 +10349,22 @@
         <v>1.68</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>45976.6875</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,73 +10417,73 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.77</v>
+        <v>1.55</v>
       </c>
       <c r="M84" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>2.37</v>
+        <v>5.2</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI84" s="3" t="n">
         <v>45976.6875</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.3</v>
+        <v>4.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -701,13 +701,13 @@
         <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
         <v>3.94</v>
@@ -716,16 +716,16 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45976.08333333334</v>
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1073,16 +1073,16 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45976.375</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="P6" t="n">
         <v>1.92</v>
@@ -1177,25 +1177,25 @@
         <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4.74</v>
       </c>
       <c r="AD6" t="n">
         <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
         <v>1.24</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1430,16 +1430,16 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45976.375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>3.06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.6</v>
@@ -1769,10 +1769,10 @@
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>2.7</v>
@@ -1793,7 +1793,7 @@
         <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
         <v>1.57</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45976.41666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.52</v>
+        <v>6.13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.23</v>
+        <v>4.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.13</v>
+        <v>2.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.28</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>4.65</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.77</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.39</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>5.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.18</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.99</v>
+        <v>3.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
         <v>3.04</v>
@@ -2831,43 +2831,43 @@
         <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>4.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45976.4375</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>3.28</v>
+        <v>2.86</v>
       </c>
       <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.26</v>
       </c>
-      <c r="V22" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45976.4375</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>4.39</v>
+        <v>1.91</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.73</v>
+        <v>5.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>8.800000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.01</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45976.4375</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45976.5</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>2.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.03</v>
+        <v>3.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45976.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.38</v>
       </c>
-      <c r="V27" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45976.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="M28" t="n">
-        <v>3.38</v>
+        <v>5.6</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45976.5</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
@@ -3902,7 +3902,7 @@
         <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
@@ -3917,10 +3917,10 @@
         <v>3.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
         <v>2.7</v>
@@ -3932,7 +3932,7 @@
         <v>1.83</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG29" t="n">
         <v>1.21</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="P30" t="n">
         <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="R30" t="n">
         <v>1.33</v>
@@ -4015,49 +4015,49 @@
         <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
         <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>2.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45976.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45976.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.95</v>
+        <v>5.13</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W32" t="n">
         <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45976.5</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.24</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="O34" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45976.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S35" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="T35" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.34</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45976.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45976.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N37" t="n">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="O37" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="P37" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.13</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="T37" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45976.5</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4.61</v>
+        <v>1.79</v>
       </c>
       <c r="O39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>45976.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45976.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.8</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V41" t="n">
-        <v>6</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>45976.5</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>17</v>
       </c>
       <c r="N42" t="n">
-        <v>2.18</v>
+        <v>46</v>
       </c>
       <c r="O42" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>45976.5</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="O43" t="n">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
         <v>1.06</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y43" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45976.5</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>45976.5</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V45" t="n">
         <v>6.5</v>
       </c>
-      <c r="O45" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>6</v>
-      </c>
-      <c r="R45" t="n">
+      <c r="W45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.32</v>
       </c>
-      <c r="S45" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V45" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AE45" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB45" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>45976.5</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>45976.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45976.5</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="M48" t="n">
         <v>3.6</v>
       </c>
       <c r="N48" t="n">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>45976.5</v>
@@ -6252,16 +6252,16 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="N49" t="n">
         <v>3.6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="P49" t="n">
         <v>2.17</v>
@@ -6276,7 +6276,7 @@
         <v>3.02</v>
       </c>
       <c r="T49" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="U49" t="n">
         <v>1.41</v>
@@ -6297,22 +6297,22 @@
         <v>3.64</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC49" t="n">
         <v>2.96</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AG49" t="n">
         <v>1.21</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="O50" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
         <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
         <v>1.36</v>
       </c>
       <c r="S50" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T50" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U50" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF50" t="n">
         <v>1.69</v>
       </c>
-      <c r="AF50" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>45976.5</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6493,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N52" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="O52" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF52" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>45976.5</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.75</v>
+        <v>1.99</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="P53" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S53" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="T53" t="n">
-        <v>3.15</v>
+        <v>2.53</v>
       </c>
       <c r="U53" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="V53" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="W53" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.95</v>
+        <v>4.16</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC53" t="n">
-        <v>4.02</v>
+        <v>3.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45976.5</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.15</v>
+        <v>1.26</v>
       </c>
       <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>11</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S55" t="n">
         <v>3.2</v>
       </c>
-      <c r="N55" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T55" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="U55" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V55" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X55" t="n">
         <v>1.03</v>
       </c>
-      <c r="X55" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.85</v>
+        <v>4.17</v>
       </c>
       <c r="AA55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB55" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AC55" t="n">
-        <v>3.54</v>
+        <v>2.49</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.66</v>
+        <v>3.38</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45976.5</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>45976.5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.49</v>
+        <v>1.84</v>
       </c>
       <c r="M57" t="n">
-        <v>3.22</v>
+        <v>3.53</v>
       </c>
       <c r="N57" t="n">
-        <v>1.8</v>
+        <v>3.39</v>
       </c>
       <c r="O57" t="n">
-        <v>4.9</v>
+        <v>2.45</v>
       </c>
       <c r="P57" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="R57" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>2.44</v>
+        <v>3.04</v>
       </c>
       <c r="T57" t="n">
-        <v>3.29</v>
+        <v>2.43</v>
       </c>
       <c r="U57" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="V57" t="n">
-        <v>8.300000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.2</v>
+        <v>2.76</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>45976.5</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="M58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N58" t="n">
         <v>3.65</v>
       </c>
-      <c r="N58" t="n">
-        <v>5.07</v>
-      </c>
       <c r="O58" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>45976.5</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.45</v>
+        <v>3.45</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>6.2</v>
+        <v>1.99</v>
       </c>
       <c r="O59" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="P59" t="n">
         <v>2</v>
       </c>
-      <c r="P59" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R59" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S59" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T59" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V59" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="W59" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X59" t="n">
         <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="AB59" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF59" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC59" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AG59" t="n">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.41</v>
+        <v>1.29</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>45976.5</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>45976.5</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>4.93</v>
       </c>
       <c r="P63" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.14</v>
+        <v>2.12</v>
       </c>
       <c r="R63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U63" t="n">
         <v>1.41</v>
       </c>
-      <c r="S63" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V63" t="n">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="W63" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.85</v>
+        <v>3.64</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.62</v>
+        <v>3.03</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>45976.5</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M64" t="n">
-        <v>3.72</v>
+        <v>3.23</v>
       </c>
       <c r="N64" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="O64" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="P64" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q64" t="n">
         <v>4.2</v>
       </c>
       <c r="R64" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S64" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="T64" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V64" t="n">
-        <v>5.85</v>
+        <v>7.3</v>
       </c>
       <c r="W64" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X64" t="n">
         <v>1.07</v>
       </c>
-      <c r="X64" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y64" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z64" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AA64" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB64" t="n">
         <v>1.74</v>
       </c>
-      <c r="AB64" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AC64" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AF64" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>45976.5</v>
@@ -8120,22 +8120,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45976.5</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="N66" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="O66" t="n">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="P66" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S66" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="T66" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U66" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V66" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="W66" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X66" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z66" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AF66" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45976.5</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S67" t="n">
         <v>2.62</v>
       </c>
-      <c r="O67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P67" t="n">
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V67" t="n">
+        <v>8</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA67" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q67" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V67" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AB67" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC67" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45976.5</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>45976.5625</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="M71" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N71" t="n">
         <v>3.25</v>
       </c>
-      <c r="N71" t="n">
-        <v>1.65</v>
-      </c>
       <c r="O71" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA71" t="n">
         <v>2.62</v>
       </c>
-      <c r="AA71" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB71" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AC71" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>45976.5625</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="O72" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45976.5625</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O73" t="n">
-        <v>2.83</v>
+        <v>6.32</v>
       </c>
       <c r="P73" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.3</v>
+        <v>2.29</v>
       </c>
       <c r="R73" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S73" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="T73" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U73" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V73" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W73" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X73" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AC73" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45976.5625</v>
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="M74" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB74" t="n">
         <v>1.5</v>
@@ -9477,10 +9477,10 @@
         <v>2.44</v>
       </c>
       <c r="P76" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R76" t="n">
         <v>1.38</v>
@@ -9516,16 +9516,16 @@
         <v>1.77</v>
       </c>
       <c r="AC76" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE76" t="n">
         <v>1.73</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG76" t="n">
         <v>1.23</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.77</v>
+        <v>4.05</v>
       </c>
       <c r="M79" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N79" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="O79" t="n">
-        <v>4.93</v>
+        <v>4.04</v>
       </c>
       <c r="P79" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="R79" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S79" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T79" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U79" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V79" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="n">
         <v>1.02</v>
       </c>
-      <c r="X79" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y79" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z79" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG79" t="n">
         <v>1.27</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45976.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="M80" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>3.23</v>
+        <v>2.6</v>
       </c>
       <c r="O80" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45976.6875</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="M81" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>4.1</v>
+        <v>4.92</v>
       </c>
       <c r="O81" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="R81" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T81" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U81" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V81" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="W81" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X81" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.65</v>
+        <v>3.27</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC81" t="n">
-        <v>4.75</v>
+        <v>3.57</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45976.6875</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,73 +10179,73 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>45976.6875</v>
@@ -10301,10 +10301,10 @@
         <v>1.4</v>
       </c>
       <c r="M83" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="N83" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="O83" t="n">
         <v>2.08</v>
@@ -10325,7 +10325,7 @@
         <v>3.1</v>
       </c>
       <c r="U83" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V83" t="n">
         <v>7.7</v>
@@ -10337,22 +10337,22 @@
         <v>1.05</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z83" t="n">
         <v>2.85</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
         <v>3.86</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE83" t="n">
         <v>2.4</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,73 +10417,73 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N84" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="O84" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="P84" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.35</v>
+        <v>2.82</v>
       </c>
       <c r="R84" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S84" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="T84" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U84" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V84" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W84" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X84" t="n">
         <v>1.07</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z84" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC84" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH84" t="n">
-        <v>2.02</v>
+        <v>1.29</v>
       </c>
       <c r="AI84" s="3" t="n">
         <v>45976.6875</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,73 +10536,73 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>45976.6875</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,73 +10774,73 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI87" s="3" t="n">
         <v>45976.70833333334</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -668,19 +668,19 @@
         <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.48</v>
+        <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
         <v>3.16</v>
@@ -701,7 +701,7 @@
         <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AA2" t="n">
         <v>2.08</v>
@@ -716,16 +716,16 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45976.08333333334</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45976.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>4.02</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45976.375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45976.375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1742,13 +1742,13 @@
         <v>3.06</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
         <v>3.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
         <v>2.27</v>
@@ -1775,13 +1775,13 @@
         <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB11" t="n">
         <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
@@ -1793,10 +1793,10 @@
         <v>1.58</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45976.39583333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2.23</v>
+        <v>4.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.13</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.16</v>
+        <v>2.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.91</v>
+        <v>6.13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4.65</v>
+        <v>1.92</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>2.59</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
         <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.69</v>
+        <v>3.73</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>3.12</v>
+        <v>2.41</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC19" t="n">
         <v>4.3</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.72</v>
+        <v>4.88</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.88</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>4.39</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.71</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45976.4375</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="T22" t="n">
-        <v>2.86</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>5.4</v>
       </c>
       <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.04</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.97</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45976.4375</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O23" t="n">
         <v>4.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.6</v>
+        <v>2.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45976.4375</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="P25" t="n">
         <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.28</v>
+        <v>4.84</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="W25" t="n">
         <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45976.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.18</v>
+        <v>3.53</v>
       </c>
       <c r="N26" t="n">
-        <v>2.67</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45976.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,37 +3634,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.9</v>
+        <v>3.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U27" t="n">
         <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>6.35</v>
+        <v>6.15</v>
       </c>
       <c r="W27" t="n">
         <v>1.06</v>
@@ -3673,10 +3673,10 @@
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA27" t="n">
         <v>1.76</v>
@@ -3685,22 +3685,22 @@
         <v>1.94</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG27" t="n">
         <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45976.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.18</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>5.6</v>
+        <v>2.91</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45976.5</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH29" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45976.5</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,55 +3991,55 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.22</v>
+        <v>2.37</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.14</v>
+        <v>4.21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
         <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
         <v>2.88</v>
@@ -4048,16 +4048,16 @@
         <v>1.32</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45976.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45976.5</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.13</v>
+        <v>4.34</v>
       </c>
       <c r="R32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.35</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V32" t="n">
-        <v>6.55</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45976.5</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45976.5</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45976.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="M35" t="n">
-        <v>2.91</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>6.66</v>
       </c>
       <c r="R35" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.02</v>
+        <v>3.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.34</v>
+        <v>2.41</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45976.5</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45976.5</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.41</v>
+        <v>17</v>
       </c>
       <c r="N37" t="n">
-        <v>3.74</v>
+        <v>46</v>
       </c>
       <c r="O37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45976.5</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N39" t="n">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>45976.5</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
         <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>45976.5</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M42" t="n">
-        <v>17</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>46</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>45976.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
-        <v>2.99</v>
+        <v>2.27</v>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>5.28</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U43" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V43" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45976.5</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>45976.5</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,37 +5776,37 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
         <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="O45" t="n">
-        <v>2.73</v>
+        <v>2.31</v>
       </c>
       <c r="P45" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.45</v>
+        <v>4.84</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S45" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T45" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U45" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W45" t="n">
         <v>1.06</v>
@@ -5815,34 +5815,34 @@
         <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD45" t="n">
         <v>1.32</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>45976.5</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>45976.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45976.5</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="M48" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="O48" t="n">
-        <v>2.76</v>
+        <v>3.72</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="R48" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="T48" t="n">
-        <v>2.53</v>
+        <v>3.16</v>
       </c>
       <c r="U48" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z48" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE48" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>45976.5</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,31 +6252,31 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
-        <v>2.38</v>
+        <v>4.99</v>
       </c>
       <c r="P49" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.21</v>
+        <v>2.13</v>
       </c>
       <c r="R49" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T49" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="U49" t="n">
         <v>1.41</v>
@@ -6291,34 +6291,34 @@
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>45976.5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="N50" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="O50" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB50" t="n">
         <v>2</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>6</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S50" t="n">
+      <c r="AC50" t="n">
         <v>2.7</v>
       </c>
-      <c r="T50" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V50" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AD50" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>45976.5</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>2.21</v>
       </c>
       <c r="M52" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>5.2</v>
+        <v>2.82</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="R52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S52" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W52" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
         <v>1.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE52" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>45976.5</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="O53" t="n">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="P53" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="T53" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="U53" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V53" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="W53" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
         <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.16</v>
+        <v>3.42</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AG53" t="n">
         <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="N54" t="n">
-        <v>1.8</v>
+        <v>3.57</v>
       </c>
       <c r="O54" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>45976.5</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>1.99</v>
       </c>
       <c r="O55" t="n">
-        <v>1.72</v>
+        <v>4.29</v>
       </c>
       <c r="P55" t="n">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="Q55" t="n">
-        <v>7.5</v>
+        <v>2.78</v>
       </c>
       <c r="R55" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="S55" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="U55" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="V55" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z55" t="n">
-        <v>4.17</v>
+        <v>2.89</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>3.38</v>
+        <v>1.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45976.5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N56" t="n">
-        <v>3.58</v>
+        <v>10</v>
       </c>
       <c r="O56" t="n">
-        <v>2.32</v>
+        <v>1.64</v>
       </c>
       <c r="P56" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z56" t="n">
+      <c r="AC56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH56" t="n">
         <v>3.44</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.88</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>45976.5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="M57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P57" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S57" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="T57" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="U57" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V57" t="n">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="W57" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
         <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z57" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>45976.5</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="M58" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>45976.5</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.45</v>
+        <v>1.39</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="N59" t="n">
-        <v>1.99</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>4.29</v>
+        <v>1.89</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S59" t="n">
-        <v>2.65</v>
+        <v>3.29</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="U59" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V59" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AC59" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.29</v>
+        <v>2.76</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>45976.5</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,34 +7561,34 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.09</v>
       </c>
       <c r="N60" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="P60" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.47</v>
+        <v>4.18</v>
       </c>
       <c r="R60" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S60" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T60" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V60" t="n">
         <v>7.1</v>
@@ -7597,37 +7597,37 @@
         <v>1.04</v>
       </c>
       <c r="X60" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG60" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>45976.5</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="M61" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="N61" t="n">
-        <v>3.21</v>
+        <v>2.45</v>
       </c>
       <c r="O61" t="n">
-        <v>2.79</v>
+        <v>3.22</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R61" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U61" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V61" t="n">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="W61" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X61" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC61" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD61" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG61" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE61" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH61" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>45976.5</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.4</v>
+        <v>1.18</v>
       </c>
       <c r="M63" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="N63" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="O63" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>45976.5</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>45976.5</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="N65" t="n">
-        <v>2.82</v>
+        <v>3.97</v>
       </c>
       <c r="O65" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="P65" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.38</v>
+        <v>5.03</v>
       </c>
       <c r="R65" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S65" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="T65" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U65" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V65" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="W65" t="n">
         <v>1.03</v>
       </c>
       <c r="X65" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z65" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45976.5</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45976.5</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="M67" t="n">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="N67" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O67" t="n">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S67" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T67" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U67" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V67" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W67" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X67" t="n">
         <v>1.06</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AG67" t="n">
         <v>1.29</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45976.5</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.65</v>
+        <v>5.3</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="O69" t="n">
-        <v>2.23</v>
+        <v>6.32</v>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.3</v>
+        <v>2.29</v>
       </c>
       <c r="R69" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S69" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="T69" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U69" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="W69" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X69" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC69" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH69" t="n">
-        <v>2.09</v>
+        <v>1.09</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45976.5625</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N70" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="O70" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="P70" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="R70" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S70" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="T70" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U70" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V70" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W70" t="n">
         <v>1.02</v>
       </c>
       <c r="X70" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AC70" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>45976.5625</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="M72" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O72" t="n">
         <v>3.55</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45976.5625</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N73" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="O73" t="n">
-        <v>6.32</v>
+        <v>2.21</v>
       </c>
       <c r="P73" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.29</v>
+        <v>6.1</v>
       </c>
       <c r="R73" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S73" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T73" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U73" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V73" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="W73" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X73" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC73" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.09</v>
+        <v>2.11</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45976.5625</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9474,7 +9474,7 @@
         <v>3.73</v>
       </c>
       <c r="O76" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="P76" t="n">
         <v>2.13</v>
@@ -9483,19 +9483,19 @@
         <v>4.33</v>
       </c>
       <c r="R76" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S76" t="n">
         <v>2.9</v>
       </c>
       <c r="T76" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U76" t="n">
         <v>1.4</v>
       </c>
       <c r="V76" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="W76" t="n">
         <v>1.04</v>
@@ -9504,7 +9504,7 @@
         <v>1.01</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z76" t="n">
         <v>3.5</v>
@@ -9519,7 +9519,7 @@
         <v>3.25</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE76" t="n">
         <v>1.73</v>
@@ -9528,10 +9528,10 @@
         <v>1.9</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>45976.60416666666</v>
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M78" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="N78" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,64 +9822,64 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4.05</v>
+        <v>2.77</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N79" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="O79" t="n">
-        <v>4.04</v>
+        <v>5.51</v>
       </c>
       <c r="P79" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.86</v>
+        <v>2.29</v>
       </c>
       <c r="R79" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S79" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T79" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U79" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V79" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W79" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X79" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC79" t="n">
-        <v>4.25</v>
+        <v>3.69</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AF79" t="n">
         <v>1.75</v>
@@ -9888,7 +9888,7 @@
         <v>1.27</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45976.6875</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N80" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45976.6875</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N81" t="n">
-        <v>4.92</v>
+        <v>7.8</v>
       </c>
       <c r="O81" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="P81" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S81" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="T81" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U81" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V81" t="n">
         <v>7.7</v>
       </c>
       <c r="W81" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X81" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y81" t="n">
         <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC81" t="n">
-        <v>3.57</v>
+        <v>3.86</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45976.6875</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,73 +10179,73 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="N82" t="n">
-        <v>1.8</v>
+        <v>3.23</v>
       </c>
       <c r="O82" t="n">
-        <v>5.01</v>
+        <v>3.4</v>
       </c>
       <c r="P82" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R82" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S82" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="T82" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V82" t="n">
+        <v>8</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y82" t="n">
         <v>1.33</v>
       </c>
-      <c r="V82" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W82" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z82" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD82" t="n">
         <v>1.21</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>45976.6875</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,73 +10298,73 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.4</v>
+        <v>2.45</v>
       </c>
       <c r="M83" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N83" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="O83" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB83" t="n">
         <v>1.6</v>
       </c>
       <c r="AC83" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>45976.6875</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,73 +10417,73 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N84" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="O84" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="P84" t="n">
         <v>1.95</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R84" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S84" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="T84" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="U84" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V84" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W84" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X84" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC84" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG84" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI84" s="3" t="n">
         <v>45976.6875</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,73 +10536,73 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="O85" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.5</v>
+        <v>5.56</v>
       </c>
       <c r="R85" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S85" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T85" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U85" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V85" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W85" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X85" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.77</v>
+        <v>3.27</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC85" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>45976.6875</v>
@@ -10804,19 +10804,19 @@
         <v>1.49</v>
       </c>
       <c r="V87" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="W87" t="n">
         <v>1.09</v>
       </c>
       <c r="X87" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z87" t="n">
-        <v>3.94</v>
+        <v>4.32</v>
       </c>
       <c r="AA87" t="n">
         <v>1.75</v>
@@ -10828,13 +10828,13 @@
         <v>2.65</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG87" t="n">
         <v>1.26</v>
@@ -10902,40 +10902,40 @@
         <v>1.28</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA88" t="n">
         <v>1.96</v>
@@ -10944,22 +10944,22 @@
         <v>1.74</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>45976.77083333334</v>
@@ -11021,40 +11021,40 @@
         <v>1.76</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA89" t="n">
         <v>1.93</v>
@@ -11063,22 +11063,22 @@
         <v>1.77</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>45976.875</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45976.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45976.375</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45976.375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45976.375</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45976.41666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.21</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.01</v>
+        <v>5.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="T14" t="n">
         <v>3.12</v>
@@ -2126,34 +2126,34 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD14" t="n">
         <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>2.71</v>
       </c>
       <c r="O15" t="n">
-        <v>4.16</v>
+        <v>3.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T15" t="n">
         <v>3.28</v>
@@ -2236,7 +2236,7 @@
         <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
@@ -2245,16 +2245,16 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
         <v>4.3</v>
@@ -2263,16 +2263,16 @@
         <v>1.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>3.17</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.23</v>
+        <v>3.98</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.13</v>
+        <v>2.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.28</v>
       </c>
-      <c r="V16" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.92</v>
+        <v>4.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.6</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.33</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.59</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="O18" t="n">
-        <v>3.73</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>2.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
         <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.03</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.93</v>
-      </c>
       <c r="Q19" t="n">
-        <v>4.45</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.86</v>
       </c>
       <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.26</v>
       </c>
-      <c r="V19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.88</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.86</v>
+        <v>2.39</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.16</v>
+        <v>1.64</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>2.86</v>
+        <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>6.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45976.4375</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.6</v>
+        <v>3.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.12</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45976.4375</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.73</v>
+        <v>6.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.86</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>8.800000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.01</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>2.59</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45976.4375</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2</v>
+        <v>1.99</v>
       </c>
       <c r="O25" t="n">
-        <v>2.08</v>
+        <v>4.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>2.69</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>6.1</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH25" t="n">
-        <v>2.42</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45976.5</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.53</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>3.39</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="P26" t="n">
         <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.48</v>
+        <v>4.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45976.5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
       <c r="P27" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>6.15</v>
+        <v>7.4</v>
       </c>
       <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.06</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45976.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45976.5</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.79</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>2.91</v>
       </c>
       <c r="N29" t="n">
-        <v>3.74</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>2.58</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.72</v>
+        <v>2.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.94</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45976.5</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.21</v>
+        <v>6.66</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
         <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45976.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.21</v>
+        <v>1.63</v>
       </c>
       <c r="O31" t="n">
-        <v>2.79</v>
+        <v>4.99</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.97</v>
+        <v>2.13</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45976.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="O32" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
         <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V32" t="n">
         <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="AD32" t="n">
         <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45976.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="P33" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.53</v>
+        <v>4.95</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>3.29</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.28</v>
       </c>
-      <c r="V33" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE33" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45976.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="T34" t="n">
         <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V34" t="n">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45976.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.55</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45976.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45976.5</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>17</v>
+        <v>5.5</v>
       </c>
       <c r="N37" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45976.5</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="M39" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.13</v>
+        <v>3.43</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="T39" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>45976.5</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.6</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.79</v>
-      </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45976.5</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>2.48</v>
+        <v>3.74</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>45976.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,31 +5419,31 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.47</v>
+        <v>4.34</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S42" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T42" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U42" t="n">
         <v>1.35</v>
@@ -5455,37 +5455,37 @@
         <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
         <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>45976.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2.27</v>
+        <v>2.53</v>
       </c>
       <c r="P43" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.28</v>
+        <v>4.47</v>
       </c>
       <c r="R43" t="n">
         <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="T43" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF43" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>45976.5</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N45" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="O45" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.84</v>
+        <v>4.48</v>
       </c>
       <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.35</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V45" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>45976.5</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>45976.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
-        <v>2.02</v>
+        <v>3.24</v>
       </c>
       <c r="P47" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.95</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S47" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T47" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U47" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="W47" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.08</v>
+        <v>3.76</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>45976.5</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="M48" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.72</v>
+        <v>4.8</v>
       </c>
       <c r="P48" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="R48" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S48" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T48" t="n">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V48" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W48" t="n">
         <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.62</v>
+        <v>4.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>45976.5</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>2.67</v>
       </c>
       <c r="O49" t="n">
-        <v>4.99</v>
+        <v>2.97</v>
       </c>
       <c r="P49" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.13</v>
+        <v>3.52</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T49" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V49" t="n">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>45976.5</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="M50" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>5.6</v>
+        <v>2.82</v>
       </c>
       <c r="O50" t="n">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="P50" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="U50" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>45976.5</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N51" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>45976.5</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="O52" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="P52" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.9</v>
+        <v>4.84</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T52" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U52" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V52" t="n">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="W52" t="n">
         <v>1.06</v>
@@ -6648,34 +6648,34 @@
         <v>1.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>45976.5</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="P53" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="U53" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V53" t="n">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>45976.5</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="N54" t="n">
-        <v>3.57</v>
+        <v>2.48</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>45976.5</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="M56" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N56" t="n">
         <v>10</v>
       </c>
       <c r="O56" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
         <v>1.49</v>
       </c>
-      <c r="V56" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AB56" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>45976.5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="M57" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="N57" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="O57" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="P57" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="R57" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U57" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="W57" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>45976.5</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2.82</v>
+        <v>1.79</v>
       </c>
       <c r="O58" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB58" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB58" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC58" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>45976.5</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>45976.5</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M60" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O60" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>45976.5</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M61" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N61" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O61" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="P61" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.8</v>
+        <v>5.13</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T61" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="U61" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V61" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W61" t="n">
         <v>1.05</v>
       </c>
       <c r="X61" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.37</v>
+        <v>2.01</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>45976.5</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="M62" t="n">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>2.77</v>
+        <v>1.89</v>
       </c>
       <c r="P62" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="R62" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S62" t="n">
-        <v>2.62</v>
+        <v>3.29</v>
       </c>
       <c r="T62" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="U62" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V62" t="n">
-        <v>7.1</v>
+        <v>5.4</v>
       </c>
       <c r="W62" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X62" t="n">
         <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.76</v>
+        <v>2.73</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.65</v>
+        <v>2.76</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>45976.5</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="M63" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>45976.5</v>
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8040,10 +8040,10 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,73 +8156,73 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>5</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V65" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE65" t="n">
         <v>1.79</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V65" t="n">
-        <v>9</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AF65" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.89</v>
+        <v>2.36</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>45976.5</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>45976.5</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>45976.5</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.3</v>
+        <v>2.17</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N69" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O69" t="n">
-        <v>6.32</v>
+        <v>3.34</v>
       </c>
       <c r="P69" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.29</v>
+        <v>3.52</v>
       </c>
       <c r="R69" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S69" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="T69" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U69" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V69" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X69" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AC69" t="n">
-        <v>4.1</v>
+        <v>4.95</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>45976.5625</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="M70" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="O70" t="n">
-        <v>3.34</v>
+        <v>2.21</v>
       </c>
       <c r="P70" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.54</v>
+        <v>6.1</v>
       </c>
       <c r="R70" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S70" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="T70" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U70" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V70" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="W70" t="n">
         <v>1.02</v>
       </c>
       <c r="X70" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC70" t="n">
-        <v>4.9</v>
+        <v>3.82</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>45976.5625</v>
@@ -8873,10 +8873,10 @@
         <v>2.3</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N71" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O72" t="n">
-        <v>3.55</v>
+        <v>6.32</v>
       </c>
       <c r="P72" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.14</v>
+        <v>2.29</v>
       </c>
       <c r="R72" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S72" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="T72" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U72" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V72" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W72" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X72" t="n">
         <v>1.04</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC72" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG72" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>45976.5625</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="M73" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O73" t="n">
         <v>3.55</v>
       </c>
-      <c r="N73" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O73" t="n">
-        <v>2.21</v>
-      </c>
       <c r="P73" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="Q73" t="n">
-        <v>6.1</v>
+        <v>3.14</v>
       </c>
       <c r="R73" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S73" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="T73" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U73" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V73" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W73" t="n">
         <v>1.02</v>
       </c>
       <c r="X73" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y73" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH73" t="n">
         <v>1.34</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>2.11</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>45976.5625</v>
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,61 +9227,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N74" t="n">
-        <v>3.8</v>
+        <v>4.53</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -9290,10 +9290,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>45976.58333333334</v>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,14 +9346,14 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N75" t="n">
         <v>3.8</v>
       </c>
-      <c r="N75" t="n">
-        <v>4.53</v>
-      </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AB75" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9587,16 +9587,16 @@
         <v>4.75</v>
       </c>
       <c r="M77" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="N77" t="n">
         <v>1.68</v>
       </c>
       <c r="O77" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="P77" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Q77" t="n">
         <v>2.14</v>
@@ -9614,16 +9614,16 @@
         <v>1.53</v>
       </c>
       <c r="V77" t="n">
-        <v>4.8</v>
+        <v>5.35</v>
       </c>
       <c r="W77" t="n">
         <v>1.09</v>
       </c>
       <c r="X77" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z77" t="n">
         <v>4.5</v>
@@ -9635,7 +9635,7 @@
         <v>2.3</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AD77" t="n">
         <v>1.46</v>
@@ -9650,7 +9650,7 @@
         <v>1.21</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>45976.61458333334</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.77</v>
+        <v>2.16</v>
       </c>
       <c r="M79" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="N79" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="O79" t="n">
-        <v>5.51</v>
+        <v>3.4</v>
       </c>
       <c r="P79" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="R79" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S79" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="T79" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U79" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V79" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W79" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X79" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="AD79" t="n">
         <v>1.21</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>45976.6875</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="M80" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N80" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="O80" t="n">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="P80" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.06</v>
+        <v>5.56</v>
       </c>
       <c r="R80" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S80" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T80" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U80" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V80" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W80" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X80" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.65</v>
+        <v>3.27</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC80" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>45976.6875</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M81" t="n">
-        <v>3.61</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>7.8</v>
+        <v>2.45</v>
       </c>
       <c r="O81" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC81" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>45976.6875</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,37 +10179,37 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="M82" t="n">
-        <v>2.89</v>
+        <v>3.61</v>
       </c>
       <c r="N82" t="n">
-        <v>3.23</v>
+        <v>7.8</v>
       </c>
       <c r="O82" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="P82" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.7</v>
+        <v>5.22</v>
       </c>
       <c r="R82" t="n">
         <v>1.44</v>
       </c>
       <c r="S82" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="T82" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U82" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V82" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="W82" t="n">
         <v>1.03</v>
@@ -10218,34 +10218,34 @@
         <v>1.04</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA82" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>45976.6875</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,73 +10298,73 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="M83" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N83" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>45976.6875</v>
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="M84" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="O84" t="n">
         <v>4.04</v>
@@ -10447,7 +10447,7 @@
         <v>1.26</v>
       </c>
       <c r="V84" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W84" t="n">
         <v>1</v>
@@ -10462,13 +10462,13 @@
         <v>2.69</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC84" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD84" t="n">
         <v>1.15</v>
@@ -10477,7 +10477,7 @@
         <v>1.92</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG84" t="n">
         <v>1.27</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,73 +10536,73 @@
         </is>
       </c>
       <c r="L85" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S85" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V85" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB85" t="n">
         <v>1.55</v>
       </c>
-      <c r="M85" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N85" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O85" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P85" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S85" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U85" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V85" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC85" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH85" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>45976.6875</v>
@@ -10655,73 +10655,73 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI86" s="3" t="n">
         <v>45976.70833333334</v>

--- a/jogos_2025-11-15.xlsx
+++ b/jogos_2025-11-15.xlsx
@@ -677,10 +677,10 @@
         <v>4.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>3.16</v>
@@ -716,13 +716,13 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.72</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45976.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45976.375</v>
@@ -1626,19 +1626,19 @@
         <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.02</v>
+        <v>4.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
         <v>9.300000000000001</v>
@@ -1650,10 +1650,10 @@
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA10" t="n">
         <v>2.25</v>
@@ -1662,22 +1662,22 @@
         <v>1.58</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>4.74</v>
       </c>
       <c r="AD10" t="n">
         <v>1.13</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45976.375</v>
@@ -1766,7 +1766,7 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
         <v>1.57</v>
@@ -1781,7 +1781,7 @@
         <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45976.41666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.2</v>
+        <v>3.11</v>
       </c>
       <c r="O14" t="n">
-        <v>2.21</v>
+        <v>2.89</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.8</v>
+        <v>3.99</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
         <v>8.1</v>
@@ -2126,34 +2126,34 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.17</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.98</v>
+        <v>2.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.89</v>
+        <v>5.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45976.41666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.88</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45976.4375</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.71</v>
+        <v>6.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>8.800000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.01</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>2.59</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45976.4375</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.23</v>
+        <v>4.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>4.88</v>
       </c>
       <c r="P19" t="n">
         <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
         <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
         <v>3.34</v>
@@ -2739,16 +2739,16 @@
         <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45976.4375</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4</v>
+        <v>6.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.3</v>
+        <v>2.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45976.4375</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="M21" t="n">
         <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>3.73</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.45</v>
+        <v>3.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
         <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45976.4375</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.73</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>3.83</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>2.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.76</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AG22" t="n">
         <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45976.4375</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC23" t="n">
         <v>4.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.59</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45976.4375</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>4.29</v>
+        <v>2.71</v>
       </c>
       <c r="P25" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.89</v>
+        <v>3.72</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45976.5</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45976.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="N27" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="O27" t="n">
-        <v>2.99</v>
+        <v>3.72</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45976.5</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.18</v>
+        <v>3.94</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.58</v>
+        <v>2.99</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="U29" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.2</v>
+        <v>2.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45976.5</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45976.5</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="O31" t="n">
-        <v>4.99</v>
+        <v>2.02</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.13</v>
+        <v>6.66</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="U31" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.12</v>
+        <v>2.41</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45976.5</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="M32" t="n">
-        <v>3.07</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>3.13</v>
+        <v>2.57</v>
       </c>
       <c r="O32" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="W32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.06</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45976.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.02</v>
+        <v>3.45</v>
       </c>
       <c r="P33" t="n">
-        <v>2.31</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.95</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45976.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="T34" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>7.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.85</v>
+        <v>3.39</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45976.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
-        <v>4.3</v>
+        <v>1.63</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45976.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45976.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="M37" t="n">
-        <v>5.5</v>
+        <v>3.18</v>
       </c>
       <c r="N37" t="n">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="O37" t="n">
-        <v>1.64</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>9.1</v>
+        <v>3.52</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U37" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.44</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45976.5</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>45976.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="O39" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="P39" t="n">
         <v>2.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.43</v>
+        <v>4.48</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="T39" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V39" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
         <v>1.21</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>45976.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.6</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.21</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
         <v>2.59</v>
       </c>
       <c r="U40" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V40" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD40" t="n">
         <v>1.32</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>45976.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="